--- a/artfynd/S 5776-2021 artfynd.xlsx
+++ b/artfynd/S 5776-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89547379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97000598</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87957278</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16575671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16575674</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16575676</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87281493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67252041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1700,6 +1745,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67252045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73281425</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1924,6 +1979,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73281434</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79864621</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2165,6 +2230,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80072637</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87868109</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2419,6 +2494,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87868730</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2546,6 +2626,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87868786</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2684,6 +2769,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87957134</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2822,6 +2912,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87957220</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2960,6 +3055,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87957251</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3081,6 +3181,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95034340</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3205,6 +3310,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102829293</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3331,6 +3441,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127617094</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3433,6 +3548,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15396149</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3541,8 +3661,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78997441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>